--- a/extenbooks/ES1304.xlsx
+++ b/extenbooks/ES1304.xlsx
@@ -921,11 +921,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_assembly</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># ES1304 — Moos vs ST Comparison 1959-1997 — PENDING</t>
+          <t># ES1304 — Moos vs ST NSW/GDP Comparison</t>
         </is>
       </c>
     </row>
@@ -1097,87 +1097,43 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: External study</t>
+          <t>**Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_assembly</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Delta: ES1301 - ES1201 over overlap 1959-2012 (54 years). Range [+1.14%, +2.38%]. Moos consistently shows HIGHER NSW than ST (i.e., Moos's reconciliation finds more positive net transfer than ST's narrow definition). The delta is small (≤2.4 pp) — the qualitative finding is robust across boundary choices.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>## Why pending</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>needs ES1201/1301</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>## Activation path</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Compute deltas between ST and Moos at overlap years</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending stub).*</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/ES1304.xlsx
+++ b/extenbooks/ES1304.xlsx
@@ -921,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 4</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1959–1997</t>
+          <t>1959-2012</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1074,54 +1074,63 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1304-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Moos 2017 vs AS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1304 — Moos vs ST NSW/GDP Comparison</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># ES1304 — Moos vs ST NSW/GDP Comparison</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Delta: ES1301 - ES1201 over overlap 1959-2012 (54 years). Range [+1.14%, +2.38%]. Moos consistently shows HIGHER NSW than ST (i.e., Moos's reconciliation finds more positive net transfer than ST's narrow definition). The delta is small (≤2.4 pp) — the qualitative finding is robust across boundary choices.</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Delta: ES1301 - ES1201 over overlap 1959-2012 (54 years). Range [+1.14%, +2.38%]. Moos consistently shows HIGHER NSW than ST (i.e., Moos's reconciliation finds more positive net transfer than ST's narrow definition). The delta is small (≤2.4 pp) — the qualitative finding is robust across boundary choices.</t>
         </is>
       </c>
     </row>
@@ -1132,6 +1141,18 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion.*</t>
         </is>
@@ -1148,10 +1169,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1176,218 +1197,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ES1304 is the Moos (2017) NSW/GDP series restricted to the 1959-1997 overlap period with Shaikh &amp; Tonak (2002). It is constructed by filtering ES1301 to years 1959-1997. The purpose is to compare the two replications directly over the period where both have coverage, and to validate that the Moos methodology faithfully reconstructs the Shaikh-Tonak series (allowing for NIPA revision differences).</t>
+          <t>The NSW series presented in this paper differs slightly from Shaikh and Tonak's series. This may be due, at least in part, because the NIPA tables were revised several times since Shaikh and Tonak's data was constructed, including a comprehensive revision in 1999. As illustrated by Figure 1, the NSW follows the same pattern in both sets of data. The differences in the series in the overlap years (1959 - 1997) are slight (approximately 1 percent of GDP).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 pp.4-5, Table 1; full_transcription.md Section 3; series_registry.json ES1304 construction</t>
+          <t>Moos 2017, Section 3, p.4-5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>overlap_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Moos Table 1 compares summary statistics for the overlap period 1959-1997. Shaikh &amp; Tonak original series: min=-2.1%, median=-0.2%, mean=0.0%, max=2.9%. Moos replicated series: min=-1.2%, median=1.0%, mean=1.1%, max=3.7%. Mean difference = 1.1 percentage points of GDP. Moos attributes this entirely to post-1999 NIPA comprehensive revision, not methodological differences. The qualitative pattern is preserved: both show approximately zero mean, both show same phase structure.</t>
+          <t>Shaikh and Tonak's series shows a minimum of -2.1% of GDP, median of -0.2%, mean of 0.0%, and maximum of 2.9%. My replicated series shows minimum of -1.2%, median of 1.0%, mean of 1.1%, and maximum of 3.7%. The mean difference is approximately 1.1 percentage points of GDP, which I attribute to NIPA revisions rather than methodological differences.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 Table 1; full_transcription.md Section 3 Extended Net Social Wage Data Series</t>
+          <t>Moos 2017, Section 3 Table 1 discussion, p.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEC-013 (2026-05-06): ST2 P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013, within 0.002 of Moos's published 0.011. The residual gap is attributable to NIPA vintage differences between our 2026 pull and Moos's ~2015 data. The V11 benchmark range for validation is [0.008, 0.018] — ST2 value of 0.013 passes. This is the primary validation criterion for ES1304.</t>
+          <t>the variation in the series is assumed to be the result of revisions of NIPA data and the series used in this paper can be considered a faithful reconstruction of Shaikh and Tonak's series.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-013</t>
+          <t>Moos 2017, Section 3, p.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>validation_logic</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ES1304 serves as the cross-validation series between study_03 (ST 2002) and study_04 (Moos 2017). If ES1304 (Moos replication, 1959-1997) closely tracks ES1201 (ST 2002 NSW/GDP, restricted to 1959-1997), then the methodology is consistent and differences between ES1201 and ES1301 beyond 1997 are genuine time-extension findings. Moos Figure 1 plots both series together showing the close overlap with a slight upward shift in the Moos series throughout (NIPA revision effect).</t>
+          <t>ES1304 is the Moos (2017) NSW/GDP series restricted to the 1959-1997 overlap period with Shaikh &amp; Tonak (2002). It is constructed by filtering ES1301 to years 1959-1997. The purpose is to compare the two replications directly over the period where both have coverage, and to validate that the Moos methodology faithfully reconstructs the Shaikh-Tonak series (allowing for NIPA revision differences).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 Figure 1; full_transcription.md Section 3</t>
+          <t>Moos_2017, Section 3 pp.4-5, Table 1; full_transcription.md Section 3; series_registry.json ES1304 construction</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>key_finding</t>
+          <t>overlap_comparison</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 1959-1997 overlap validates the Moos replication. Differences between the two series are approximately 1 percentage point of GDP throughout (NIPA vintage effect). Most importantly: Shaikh &amp; Tonak show some years with slightly negative NSW in the 1980s-1990s; Moos's revised series shows these same years as slightly positive. This is the most significant qualitative difference — the Reagan-Bush era may show a slightly less negative NSW with the revised NIPA data. By 2000, NSW/GDP = ~0.0065 in Moos (approximately zero), consistent with the long-run Shaikh-Tonak finding.</t>
+          <t>Moos Table 1 compares summary statistics for the overlap period 1959-1997. Shaikh &amp; Tonak original series: min=-2.1%, median=-0.2%, mean=0.0%, max=2.9%. Moos replicated series: min=-1.2%, median=1.0%, mean=1.1%, max=3.7%. Mean difference = 1.1 percentage points of GDP. Moos attributes this entirely to post-1999 NIPA comprehensive revision, not methodological differences. The qualitative pattern is preserved: both show approximately zero mean, both show same phase structure.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3 pp.4-5; full_transcription.md Section 3</t>
+          <t>Moos_2017, Section 3 Table 1; full_transcription.md Section 3 Extended Net Social Wage Data Series</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>phase_context</t>
+          <t>decision_reference</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Within the 1959-1997 overlap window, both series show the same three-phase structure documented by Shaikh &amp; Tonak (2002): (1) negative/near-zero NSW during boom 1959-1969; (2) sharp rise to peak positive ~1975; (3) secular decline through Reagan-Bush era returning to near zero by 1997. The Moos series shows the 1980s period as less negative than Shaikh-Tonak's original — attributable to revised NIPA data showing higher benefits or lower taxes in retrospect.</t>
+          <t>[internal-decision-record] (2026-05-06): ST2 P21 achieves 1959-1997 overlap mean NSW/GDP = 0.013, within 0.002 of Moos's published 0.011. The residual gap is attributable to NIPA vintage differences between our 2026 pull and Moos's ~2015 data. The V11 benchmark range for validation is [0.008, 0.018] — ST2 value of 0.013 passes. This is the primary validation criterion for ES1304.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Moos_2017, Section 3, Figure 1; ST_2002 Figs 29.2-29.3; full_transcription.md Section 3</t>
+          <t>[internal-decision-log] [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>validation_logic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ES1304 = ES1301 filtered to year range [1959, 1997]. Construction: filter(ES1301, year &lt;= 1997). No additional computation. Year 1997 is last year of Shaikh-Tonak (2002) coverage and the overlap endpoint. Moos extends to 2012 in ES1301/ES1302; ES1304 isolates the period of joint coverage for direct comparison with ES1201.</t>
+          <t>ES1304 serves as the cross-validation series between study_03 (ST 2002) and study_04 (Moos 2017). If ES1304 (Moos replication, 1959-1997) closely tracks ES1201 (ST 2002 NSW/GDP, restricted to 1959-1997), then the methodology is consistent and differences between ES1201 and ES1301 beyond 1997 are genuine time-extension findings. Moos Figure 1 plots both series together showing the close overlap with a slight upward shift in the Moos series throughout (NIPA revision effect).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>series_registry.json ES1304 construction step 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Moos_2017, Section 3 Figure 1; full_transcription.md Section 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>key_finding</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The 1959-1997 overlap validates the Moos replication. Differences between the two series are approximately 1 percentage point of GDP throughout (NIPA vintage effect). Most importantly: Shaikh &amp; Tonak show some years with slightly negative NSW in the 1980s-1990s; Moos's revised series shows these same years as slightly positive. This is the most significant qualitative difference — the Reagan-Bush era may show a slightly less negative NSW with the revised NIPA data. By 2000, NSW/GDP = ~0.0065 in Moos (approximately zero), consistent with the long-run Shaikh-Tonak finding.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 3 pp.4-5; full_transcription.md Section 3</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>phase_context</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ES1304 is ES1301 restricted to 1959-1997, enabling direct comparison with ST 2002 coverage. Moos's replicated series shows mean 1.1% of GDP vs Shaikh-Tonak original mean 0.0% — difference attributed to post-1999 NIPA revision. ST2 achieves 0.013 vs Moos published 0.011, within V11 benchmark range [0.008, 0.018].</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
+          <t>Within the 1959-1997 overlap window, both series show the same three-phase structure documented by Shaikh &amp; Tonak (2002): (1) negative/near-zero NSW during boom 1959-1969; (2) sharp rise to peak positive ~1975; (3) secular decline through Reagan-Bush era returning to near zero by 1997. The Moos series shows the 1980s period as less negative than Shaikh-Tonak's original — attributable to revised NIPA data showing higher benefits or lower taxes in retrospect.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Moos_2017, Section 3, Figure 1; ST_2002 Figs 29.2-29.3; full_transcription.md Section 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ES1304 = ES1301 filtered to year range [1959, 1997]. Construction: filter(ES1301, year &lt;= 1997). No additional computation. Year 1997 is last year of Shaikh-Tonak (2002) coverage and the overlap endpoint. Moos extends to 2012 in ES1301/ES1302; ES1304 isolates the period of joint coverage for direct comparison with ES1201.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>series_registry.json ES1304 construction step 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The ~1.1 pp systematic upward shift vs Shaikh-Tonak original is documented and expected (NIPA revision effect)</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES1304 inherits all caveats from ES1301 (DEC-013 E2 exclusion, NIPA vintage gap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>The NSW series presented in this paper differs slightly from Shaikh and Tonak's series. This may be due, at least in part, because the NIPA tables were revised several times since Shaikh and Tonak's data was constructed, including a comprehensive revision in 1999. As illustrated by Figure 1, the NSW follows the same pattern in both sets of data. The differences in the series in the overlap years (1959 - 1997) are slight (approximately 1 percent of GDP).</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Shaikh and Tonak's series shows a minimum of -2.1% of GDP, median of -0.2%, mean of 0.0%, and maximum of 2.9%. My replicated series shows minimum of -1.2%, median of 1.0%, mean of 1.1%, and maximum of 3.7%. The mean difference is approximately 1.1 percentage points of GDP, which I attribute to NIPA revisions rather than methodological differences.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>the variation in the series is assumed to be the result of revisions of NIPA data and the series used in this paper can be considered a faithful reconstruction of Shaikh and Tonak's series.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ES1304 is ES1301 restricted to 1959-1997, enabling direct comparison with ST 2002 coverage. Moos's replicated series shows mean 1.1% of GDP vs Shaikh-Tonak original mean 0.0% — difference attributed to post-1999 NIPA revision. ST2 achieves 0.013 vs Moos published 0.011, within V11 benchmark range [0.008, 0.018].</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The ~1.1 pp systematic upward shift vs Shaikh-Tonak original is documented and expected (NIPA revision effect)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES1304 inherits all caveats from ES1301 ([internal-decision-record] E2 exclusion, NIPA vintage gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>cross_references:</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
         <is>
           <t>ES1301</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>ES1201</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
         <is>
           <t>ES1202</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Moos, Katherine A. 2017. 'Neoliberal Redistributive Policy: The U.S. Net Social Wage in the 21st Century.' Working Paper No. 2017-18, Department of Economics, University of Massachusetts Amherst. September 18, 2017.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>ST_2002</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism. M.E. Sharpe, Armonk. pp. 247-265.</t>
         </is>
@@ -1404,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1471,7 +1580,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1997": 0.011}</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1625,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
